--- a/data/trans_orig/IP07C09-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07C09-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido hablar de todos sus amigos en 2007 (tasa de respuesta: 89,49%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as en 2007 (tasa de respuesta: 89,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17868</t>
+          <t>18078</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30398</t>
+          <t>29492</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17092</t>
+          <t>17370</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29963</t>
+          <t>29356</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38316</t>
+          <t>39003</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56365</t>
+          <t>56092</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>44,97%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23916</t>
+          <t>23834</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36370</t>
+          <t>35715</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34945</t>
+          <t>34782</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47635</t>
+          <t>47538</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>61880</t>
+          <t>62041</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>80079</t>
+          <t>79577</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>63,79%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>754</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>634</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10453</t>
+          <t>11008</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32600</t>
+          <t>31451</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48416</t>
+          <t>47360</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31770</t>
+          <t>31957</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>46770</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68394</t>
+          <t>68552</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>90096</t>
+          <t>90734</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,77%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42853</t>
+          <t>43857</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58626</t>
+          <t>59131</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33046</t>
+          <t>32774</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48221</t>
+          <t>47518</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>81145</t>
+          <t>80834</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>102901</t>
+          <t>102203</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>53,81%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11283</t>
+          <t>11951</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15950</t>
+          <t>15779</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11885</t>
+          <t>11736</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>24733</t>
+          <t>24268</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3281</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3412</t>
+          <t>3398</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4073</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25392</t>
+          <t>25481</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36851</t>
+          <t>36476</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29364</t>
+          <t>29308</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40965</t>
+          <t>41849</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57907</t>
+          <t>58798</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74370</t>
+          <t>74626</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>64,16%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15648</t>
+          <t>15326</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26534</t>
+          <t>26539</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15965</t>
+          <t>15486</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27468</t>
+          <t>27317</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34125</t>
+          <t>33988</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49234</t>
+          <t>49490</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,55%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>6837</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7644</t>
+          <t>7918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3716</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11554</t>
+          <t>11384</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>3344</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22565</t>
+          <t>22951</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>36813</t>
+          <t>37424</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30755</t>
+          <t>31004</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45929</t>
+          <t>46402</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57326</t>
+          <t>57417</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>78150</t>
+          <t>78493</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>47,16%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30321</t>
+          <t>29920</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45154</t>
+          <t>44661</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>32351</t>
+          <t>32841</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47656</t>
+          <t>47565</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>67464</t>
+          <t>67491</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>88308</t>
+          <t>88555</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>53,21%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5617</t>
+          <t>5204</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15827</t>
+          <t>15262</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>5892</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16070</t>
+          <t>15455</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13831</t>
+          <t>13584</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>28821</t>
+          <t>27033</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>16,24%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4178</t>
+          <t>4894</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>112389</t>
+          <t>112035</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>138787</t>
+          <t>138598</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>123651</t>
+          <t>122870</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>149810</t>
+          <t>149748</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>241035</t>
+          <t>240837</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>281190</t>
+          <t>280067</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,88%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>124994</t>
+          <t>125639</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>152734</t>
+          <t>153669</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>127681</t>
+          <t>129111</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>155918</t>
+          <t>156832</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>261406</t>
+          <t>264766</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>299855</t>
+          <t>303881</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,86%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16007</t>
+          <t>16542</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>30136</t>
+          <t>31882</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>19285</t>
+          <t>19792</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>36049</t>
+          <t>35501</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>39665</t>
+          <t>40174</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>61561</t>
+          <t>61424</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>674</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6558</t>
+          <t>7063</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5757</t>
+          <t>4729</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8762</t>
+          <t>8894</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido hablar de todos sus amigos en 2012 (tasa de respuesta: 95,1%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as en 2012 (tasa de respuesta: 95,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28069</t>
+          <t>27571</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40912</t>
+          <t>41019</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31440</t>
+          <t>31391</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46021</t>
+          <t>45467</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63485</t>
+          <t>63652</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82629</t>
+          <t>82254</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,38%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14699</t>
+          <t>15015</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27454</t>
+          <t>27484</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20025</t>
+          <t>20509</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34660</t>
+          <t>33940</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38646</t>
+          <t>39120</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56711</t>
+          <t>57733</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>43,08%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9405</t>
+          <t>9961</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6555</t>
+          <t>6799</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4261</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13844</t>
+          <t>13838</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3526</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4092</t>
+          <t>4207</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>646</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5926</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>5480</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4654</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>694</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>6889</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42342</t>
+          <t>41818</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58676</t>
+          <t>57851</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42427</t>
+          <t>43358</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58419</t>
+          <t>58081</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>89659</t>
+          <t>88372</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111181</t>
+          <t>111318</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>57,86%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29274</t>
+          <t>29640</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44553</t>
+          <t>45197</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28558</t>
+          <t>28653</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43125</t>
+          <t>43351</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>62837</t>
+          <t>61795</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>84050</t>
+          <t>84713</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>44,03%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5142</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13717</t>
+          <t>14285</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11101</t>
+          <t>10813</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9797</t>
+          <t>9766</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>21716</t>
+          <t>21978</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>2590</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>626</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5308</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8067</t>
+          <t>7743</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26431</t>
+          <t>26784</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39175</t>
+          <t>39138</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38718</t>
+          <t>38753</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51241</t>
+          <t>51454</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69302</t>
+          <t>68947</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>86576</t>
+          <t>87841</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>65,72%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17880</t>
+          <t>18059</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30472</t>
+          <t>30025</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12332</t>
+          <t>12122</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23575</t>
+          <t>23646</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33194</t>
+          <t>33203</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50157</t>
+          <t>50841</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>38,04%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10861</t>
+          <t>10540</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1596</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8166</t>
+          <t>8577</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5635</t>
+          <t>5775</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15652</t>
+          <t>15694</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>591</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>5202</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7499</t>
+          <t>7590</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2917</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37123</t>
+          <t>36391</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53198</t>
+          <t>52575</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39604</t>
+          <t>40023</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55746</t>
+          <t>55403</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>84000</t>
+          <t>82172</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>105079</t>
+          <t>104264</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,03%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26459</t>
+          <t>25911</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>41930</t>
+          <t>42266</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>23846</t>
+          <t>24154</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>38861</t>
+          <t>39255</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>54642</t>
+          <t>54546</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>74358</t>
+          <t>76613</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>44,11%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1858</t>
+          <t>2267</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10547</t>
+          <t>10665</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14576</t>
+          <t>14990</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8095</t>
+          <t>8713</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21040</t>
+          <t>21094</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -6799,7 +6799,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>3718</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3824</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3609</t>
+          <t>3530</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>146711</t>
+          <t>149445</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>176647</t>
+          <t>179201</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>165415</t>
+          <t>166109</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>196914</t>
+          <t>194846</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>323956</t>
+          <t>324900</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>365437</t>
+          <t>366658</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,86%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>101920</t>
+          <t>100128</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>130336</t>
+          <t>127750</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>98940</t>
+          <t>97458</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>125690</t>
+          <t>126446</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>207592</t>
+          <t>207175</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>246931</t>
+          <t>244762</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,62%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17860</t>
+          <t>17531</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>33817</t>
+          <t>33132</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15599</t>
+          <t>15998</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>30668</t>
+          <t>30337</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>37379</t>
+          <t>36830</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>58702</t>
+          <t>58757</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>7136</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>7714</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3829</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>11571</t>
+          <t>12804</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>9845</t>
+          <t>9777</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>13442</t>
+          <t>13854</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido hablar de todos sus amigos en 2016 (tasa de respuesta: 95,28%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as en 2016 (tasa de respuesta: 95,28%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33471</t>
+          <t>32607</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47276</t>
+          <t>47170</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34777</t>
+          <t>35388</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49292</t>
+          <t>49509</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>72838</t>
+          <t>72401</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>92769</t>
+          <t>93007</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,41%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16796</t>
+          <t>17333</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30090</t>
+          <t>30917</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12578</t>
+          <t>12716</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25544</t>
+          <t>25753</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32900</t>
+          <t>33576</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51636</t>
+          <t>51750</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,95%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1632</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>9078</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4961</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15023</t>
+          <t>14758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7928</t>
+          <t>8585</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20083</t>
+          <t>20322</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4084</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>3909</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48438</t>
+          <t>48268</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65740</t>
+          <t>64429</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49483</t>
+          <t>49503</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65669</t>
+          <t>65978</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>102480</t>
+          <t>104179</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>125633</t>
+          <t>126369</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>61,86%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26049</t>
+          <t>27191</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42013</t>
+          <t>42423</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28600</t>
+          <t>28617</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44441</t>
+          <t>43880</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59080</t>
+          <t>58768</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80548</t>
+          <t>80450</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,38%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15172</t>
+          <t>15794</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9315</t>
+          <t>8508</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9278</t>
+          <t>9358</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>21646</t>
+          <t>21029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>606</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6496</t>
+          <t>5927</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>713</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6655</t>
+          <t>6676</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4374</t>
+          <t>3761</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4635</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5836</t>
+          <t>6714</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38105</t>
+          <t>37269</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50664</t>
+          <t>51161</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37898</t>
+          <t>37736</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52001</t>
+          <t>51919</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>78677</t>
+          <t>78603</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97269</t>
+          <t>98957</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>68,75%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15406</t>
+          <t>15168</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27572</t>
+          <t>27452</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17955</t>
+          <t>18898</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31752</t>
+          <t>32392</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37474</t>
+          <t>36791</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55626</t>
+          <t>55371</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,47%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>2071</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9158</t>
+          <t>9448</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>749</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7259</t>
+          <t>7964</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14426</t>
+          <t>13139</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>2997</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2771</t>
+          <t>2789</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53853</t>
+          <t>54174</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>71658</t>
+          <t>71610</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52529</t>
+          <t>53643</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>69540</t>
+          <t>69757</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>112610</t>
+          <t>112890</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>135443</t>
+          <t>135917</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,82%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20484</t>
+          <t>20567</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>35852</t>
+          <t>36953</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>19338</t>
+          <t>19275</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>34459</t>
+          <t>33735</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>43924</t>
+          <t>43514</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>65077</t>
+          <t>64635</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,78%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5656</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16902</t>
+          <t>16222</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6707</t>
+          <t>6639</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18069</t>
+          <t>17624</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14578</t>
+          <t>14462</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29204</t>
+          <t>30298</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -10401,82 +10401,82 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>6536</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>6,29%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>2355</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
           <t>767</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>6442</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>6,2%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>2355</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>770</t>
-        </is>
-      </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6185</t>
+          <t>7061</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10554,7 +10554,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5091</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>188591</t>
+          <t>188942</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>219781</t>
+          <t>219907</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>192969</t>
+          <t>192035</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>221476</t>
+          <t>221772</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>389288</t>
+          <t>390803</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>434426</t>
+          <t>434316</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>62,79%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>93190</t>
+          <t>91155</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>121084</t>
+          <t>121751</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>90945</t>
+          <t>91284</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>119181</t>
+          <t>120261</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>190006</t>
+          <t>191305</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>230938</t>
+          <t>231753</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,5%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>21476</t>
+          <t>21560</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>38627</t>
+          <t>38650</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>20878</t>
+          <t>20120</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>38106</t>
+          <t>36633</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>45268</t>
+          <t>46098</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>70496</t>
+          <t>70166</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8028</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8134</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>3598</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>13464</t>
+          <t>13324</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>5620</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>639</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10021</t>
+          <t>9521</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
